--- a/output/pdf_financials_xlsx/OLY.xlsx
+++ b/output/pdf_financials_xlsx/OLY.xlsx
@@ -6920,7 +6920,7 @@
         <v>0.08637300000000001</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>86373</v>
+        <v>172746</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0.08637300000000001</v>

--- a/output/pdf_financials_xlsx/OLY.xlsx
+++ b/output/pdf_financials_xlsx/OLY.xlsx
@@ -7384,19 +7384,19 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.127891</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>162957</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>382238</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.306817</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.336726</v>
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
@@ -70616,7 +70616,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -72298,7 +72298,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -74698,7 +74698,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">

--- a/output/pdf_financials_xlsx/OLY.xlsx
+++ b/output/pdf_financials_xlsx/OLY.xlsx
@@ -5557,22 +5557,22 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.907066</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>184474</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.389348</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.5060210000000001</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.471192</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>0.2236</v>
       </c>
     </row>
     <row r="71">
@@ -5618,22 +5618,22 @@
         <v>4.207347</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6.655347</v>
+        <v>7.562413</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>12382366</v>
+        <v>12566840</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>4.953278</v>
+        <v>5.342626</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.565889</v>
+        <v>3.07191</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.79579</v>
+        <v>2.266982</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>0.2236</v>
       </c>
     </row>
     <row r="72">
@@ -5862,22 +5862,22 @@
         <v>1.694195</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>3.474006</v>
+        <v>2.56694</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>2677490</v>
+        <v>2493016</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>3.950508</v>
+        <v>3.56116</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>6.48944</v>
+        <v>5.983419</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.740765</v>
+        <v>2.269573</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>2.169197</v>
+        <v>1.945597</v>
       </c>
     </row>
     <row r="76">
@@ -6189,24 +6189,22 @@
         <v>0.2789857506203058</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.3712108970904774</v>
+        <v>0.4218037187089852</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.6595764208452588</v>
+        <v>0.669402870867735</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.195607478381216</v>
+        <v>0.2109830297822821</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.07264356146644421</v>
+        <v>0.08696965570388455</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.04284358651819962</v>
-      </c>
-      <c r="S80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05408518782942394</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0.005030979788038702</v>
       </c>
     </row>
     <row r="81">
@@ -12394,7 +12392,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -12778,7 +12780,11 @@
           <t>Lease liabilities $</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -82736,7 +82742,11 @@
           <t>EARNINGS FROM OPERATIONS</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr">
         <is>
           <t>-</t>
